--- a/excel/atuq-dex-s-a-c_ruta_proxima_semana.xlsx
+++ b/excel/atuq-dex-s-a-c_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$361</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J343"/>
+  <dimension ref="A1:J361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9786,7 +9786,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9801,22 +9801,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>C001411820</t>
+          <t>C001689918</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>10402545823</t>
+          <t>02832967</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C001411820 - BRAVO VILELA EDITH CONSUELO</t>
+          <t>INFANTE MELGAR CARMEN DEL PILAR</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9826,19 +9826,19 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>JR. MARISCAL RAMON CASTILLA(POR EL NRO. 506 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. AAHH ALIPIO ROSALES PUYANGO MZA. B LOTE. 13 URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9853,22 +9853,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>C001572495</t>
+          <t>C001730093</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>47188882</t>
+          <t>10414649284</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001572495 - NUNEZ JARA JOSE ELIZARDO</t>
+          <t>VARGAS BURGOS PAOLA CAROLINA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9878,19 +9878,19 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>PJE. EL MERCADO NRO. 104 Tumbes-Zarumilla-Zarumilla</t>
+          <t>JR. LOS ANGELES NRO. 206 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>C001413115</t>
+          <t>C001032239</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>00370206</t>
+          <t>10003717017</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001413115 - FARIAS DE RUIZ FABIOLA NOEMI</t>
+          <t>RAMOS ALVINES FILONILA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9930,19 +9930,19 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>MCDO. MCDO ZARUMILLA (INTERIOR ) URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>MERCADO PSTO. 05 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9957,22 +9957,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>C001526507</t>
+          <t>C001409059</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>45323624</t>
+          <t>20409410961</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001526507 - ZURITA JIMENEZ EDINSON</t>
+          <t>EMP.INNOVA ROMERO S.R.L.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9982,19 +9982,19 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>AV. EX MERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AH ALIPIO ROSALES CAMACHO (F MZA. F LOTE. 07 URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10009,44 +10009,44 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>C004193771</t>
+          <t>C004214084</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>80273095</t>
+          <t>10451986088</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C004193771 - TABOADA ZETA JOSE MANUEL</t>
+          <t>ROSALES NORIEGA NADIA MILETH</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>TUMBES</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psj el mercado N 108 cent Zarumilla </t>
+          <t>-call.las américas s/n mz D prima lt26</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10061,22 +10061,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>C001768136</t>
+          <t>C001768361</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>10774237394</t>
+          <t>43842271</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>C001768136 - LINARES SUAREZ ANGELA PATRICIA</t>
+          <t>ALBURQUEQUE PALOMINO DENNY</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -10086,19 +10086,19 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>CL. LETICIAS -EXT MERCADO ZARUMIL URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. JACINTO SEMINARIO PUYANGO URB. FRENTE AL MERCADO PSTO. 3-4 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>C004100567</t>
+          <t>C004181522</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>45823572</t>
+          <t>61346866</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>C004100567 - MATEO MAZA MADALI</t>
+          <t>JULCA VALENCIA CINTHYA PAOLA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -10138,19 +10138,19 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Mcdo. Zarumilla Psto. 24</t>
+          <t>C. Jacinto seminario s/n</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>C001768018</t>
+          <t>C001714005</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>74802061</t>
+          <t>70665506</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>C001768018 - CEDILLO LOPEZ LORENA DEL PILAR</t>
+          <t>SANDOVAL SANTISTEBAN LUIS ALBERTO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10190,19 +10190,19 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>MCDO. BODEGA NRO. 5 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. VIRGEN DEL CISNE MZA. E LOTE. 21 URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10217,22 +10217,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>C001157395</t>
+          <t>C001630774</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>03706464</t>
+          <t>10176349862</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C001157395 - TALLEDO PE A LUCY</t>
+          <t>MARIA LAURA SANTISTEBAN RECOBA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10242,19 +10242,19 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>MERCADO DE ZARUMILLA URB. INTERIOR DE MERCADO PSTO. 09 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. EXT MERCADO PUYANGO URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -10269,22 +10269,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>C001400704</t>
+          <t>C001162218</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>00205425</t>
+          <t>10002082476</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001400704 - GOMEZ DE SERNA ANITA MARIA</t>
+          <t>HUAMAN HUACCHILLO FELICIANA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10294,19 +10294,19 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>AV. INDEPENDENCIA NRO. 440 URB. CERCA A RADIO ACTIVA Tumbes-Zarumilla-Zarumilla</t>
+          <t>PUESTO NRO 66 NRO. 67 URB. INTERIOR MERCADO PSTO. 66 - 6 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>C004172505</t>
+          <t>C001768273</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>72412079</t>
+          <t>00249512</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C004172505 - CORDOVA CORDOVA HERLINDA</t>
+          <t>YOVERA PURUGUAY MARIA DORIS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -10346,19 +10346,19 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Int. Mercado zarumilla </t>
+          <t>AV. ANDRES ARAUJO MZA. 28 LOTE. A-05 URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>C001378048</t>
+          <t>C001630694</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>00371065</t>
+          <t>77171351</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001378048 - DELGADO SANCHEZ MELIDORO</t>
+          <t>CRUZ NUNEZ FRANCISCO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10398,19 +10398,19 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO ZARUMILLA S/N URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. AAHH VIRGENDEL CISNE MZA. B LOTE. 12 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>C001018186</t>
+          <t>C001424249</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>10003627425</t>
+          <t>10002544895</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C001018186 - GARAY GONZALES FRANCISCO</t>
+          <t>YOVERA PURUGUAY RAQUEL ARACELI</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10450,19 +10450,19 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>MCDO. INT MERCADO ZARUMILLA URB. ZARUMILLA PSTO. 12 Tumbes-Zarumilla-Zarumilla</t>
+          <t>CL. JACINTO SEMINARIO MZA. 27 LOTE. 17 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10477,22 +10477,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>C001435909</t>
+          <t>C004174038</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>17143614646</t>
+          <t>45867754</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C001435909 - DIAZ CHEVEZ ASTERIO</t>
+          <t>MORALES ABAD GIOVANI ELIZABETH</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -10502,19 +10502,19 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>MCDO. PUESTO 06 MERCADO DE ZARUMILLA PSTO. 06 Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">C. Santo domingo 27-13 </t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>C001158706</t>
+          <t>C001689915</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>00369960</t>
+          <t>00251139</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C001158706 - DELGADO SANCHEZ JESUS MARIA</t>
+          <t>ORTIZ PANGALIMA SEGUNDO GERMAN</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -10554,19 +10554,19 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>MERCADO DE ZARUMILLA URB. ZARUMILLA PSTO. 30 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. EL EJERCITO NRO. 133 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10581,22 +10581,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>C001479795</t>
+          <t>C004219864</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>00371288</t>
+          <t>20615159221</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C001479795 - ZETA NAMUCHE ZAIDA ADRIANA</t>
+          <t>MARKET 'FRUTERIA &amp; VERDULERIA' SR. FRUTA E.I.R.L.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -10606,19 +10606,19 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO ZARUMILLA NRO. 6 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. BELAUNDE TERRY INT. 2 LT. 1 MZ. 25 URB. ANDRESD9410296009007</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>C001130585</t>
+          <t>C004192831</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>16445546</t>
+          <t>00206988</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>C001130585 - MAZA ZURITA SANTOS</t>
+          <t>OYOLA BENAVIDES CLARA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -10658,19 +10658,19 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>AV. INTERIOR MERCADO ZARUMILLA URB. COSTADO DE ZURITA HUAMAN PSTO. 24 Tumbes-Zarumilla-Zarumilla</t>
+          <t>Psj,santa rosa mzf lt23</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10685,22 +10685,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>C001730092</t>
+          <t>C001768406</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>00361652</t>
+          <t>10002529918</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>C001730092 - TALLEDO PENA REYNA YSABEL</t>
+          <t>ZARATE QUINTANA MARIA ERLA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -10710,19 +10710,19 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>AV. TUPAC AMARU NRO. 242 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. AA HH JPSE LISNHER TUDELA MZA. F LOTE. 19 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>C001672622</t>
+          <t>C001766790</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>43037512</t>
+          <t>72214494</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>C001672622 - DIOSES CUEVA DIOVALDO CLIMER</t>
+          <t>SOTO HERNANDEZ MERCEDES YAMILE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10762,19 +10762,19 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>AV. PRINCIPAL NRO. 223 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. CARLOS ALBERTO LINDAO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10789,22 +10789,22 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>C001742395</t>
+          <t>C001648364</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>00364920</t>
+          <t>10027963779</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>C001742395 - VILELA NOLE CESAR ANTONIO</t>
+          <t>HERNANDEZ PACHERRES SEGUNDO MIGUEL</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10814,19 +10814,19 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>AV. MERCADO DE ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>CALLE LAS GARDENIAS NRO. 188 URB. URB LISHNER TUDELA Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10841,22 +10841,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>C001366914</t>
+          <t>C001407725</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>00369656</t>
+          <t>10032350092</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C001366914 - ZURITA MATEO FAUSTINO</t>
+          <t>BAUTISTA GARCIA TITO SANTOS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10866,19 +10866,19 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>MCDO. ZARUMILLA INT. 15 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>CL. AH EL ROBLE (COSTDO DE COLE MZA. Y LOTE. 03 URB. PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10893,22 +10893,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>C001420887</t>
+          <t>C001768338</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>10003712007</t>
+          <t>80290590</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>C001420887 - SALAZAR ATOCHE ESTHERCITA DINORA</t>
+          <t>RODRIGUEZ AREVALO ERMELINDA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10918,19 +10918,19 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO MODELO (ENTRADA PRINCI URB. ZARUMILLA PSTO. 28 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AAHH ANDRES AVELINO CACERES MZA. A LOTE. 12 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>C004213910</t>
+          <t>C001502161</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>72675537</t>
+          <t>80381727</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>C004213910 - RUGEL AMAYA MONICA MARGOT</t>
+          <t>CORREA MOROCHO EMERITA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -10970,19 +10970,19 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Exterior mercado zarumilla - zarumilla</t>
+          <t>CL. SAN PEDRO MZA. H LOTE. 3 URB. LOS ANGELES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>C001674095</t>
+          <t>C001768397</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>74845473</t>
+          <t>10002538500</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>C001674095 - REYES IZQUIERDO JOSEPH DARWIN</t>
+          <t>BALLADARES VILLAR VDA DE NAVARRO LUCY BE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -11022,19 +11022,19 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>AV. MERCADO DE ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. AAHH LOS ANGELES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11049,22 +11049,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>C004168510</t>
+          <t>C001485647</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>03209306</t>
+          <t>10414713454</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C004168510 - MEZA VASQUEZ JORGE ALFREDO</t>
+          <t>CLAVIJO MIRANDA MERCEDES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -11074,19 +11074,19 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercado Santa Rosa </t>
+          <t>AV. URB JOSE LISHNER TUDELA MZA. K LOTE. 7 URB. URB JOSE L TUDELA - PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11101,22 +11101,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>C001682231</t>
+          <t>C004191453</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>45791115</t>
+          <t>10002049398</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001682231 - OYOLA ALVITES JUAN DANIEL</t>
+          <t>AGURTO VELASQUEZ DE FARIAS CELIA MERCEDE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -11126,19 +11126,19 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>AV. EX MERCADO ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>-urb,jose lisner tutela mz,h prima lt 14</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>C001722629</t>
+          <t>C001025624</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>41317230</t>
+          <t>17610068</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C001722629 - CAMPOS SEMINARIO LIZ LORENA</t>
+          <t>CAMPOS GARCIA PATRICIA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -11178,19 +11178,19 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>JR. FRANSISCO BOLOGNESI ZARUMILL NRO. 505 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>CL. JACINTO SEMINARIO MZA. Y LOTE. 08 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11205,22 +11205,22 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>C001689498</t>
+          <t>C001515311</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>42984191</t>
+          <t>10002475702</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>C001689498 - MAZA HUAMAN DUBER</t>
+          <t>CRUZ SANTOS JUANA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -11230,19 +11230,19 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>AV. EXT MERCADO DE ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. PUYANGO MZA. P LOTE. 14 URB. URB JOSE LISHNER TUDELA Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>C001767082</t>
+          <t>C001400849</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>10003713500</t>
+          <t>10002459511</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C001767082 - PORRAS SALDARRIAGA YUBICCY YICEL</t>
+          <t>OGONA JIMENEZ SANTOS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -11282,19 +11282,19 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>AV. MERCADO DE ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AH ANDRES A CACERES MZA. H LOTE. 09 URB. COSTADO PLATAFORMA DEPORTIVA Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-27 00:00:00</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>C004184162</t>
+          <t>C004192444</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>71747219</t>
+          <t>43060834</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C004184162 - CRIOLLO PORRAS JULIO ANTONIO</t>
+          <t>JIMENEZ RIVERA CARMITA YANET</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -11334,19 +11334,19 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Zarumilla (Zarumilla)</t>
+          <t>Tumbes (Tumbes)</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarumilla, mercado x menestras </t>
+          <t>AA HH Andrés avelino Cáceres Mz ll Lt 06 ca Alfons</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11361,22 +11361,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>C004217946</t>
+          <t>C001411820</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>00373511</t>
+          <t>10402545823</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004217946 - GEORGINA ELIZABETH TUPEZ BURGOS</t>
+          <t>C001411820 - BRAVO VILELA EDITH CONSUELO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -11391,14 +11391,14 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Calle gardenias s/N esq con geranios/rest tollo</t>
+          <t>JR. MARISCAL RAMON CASTILLA(POR EL NRO. 506 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11413,22 +11413,22 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>C001410731</t>
+          <t>C001572495</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>10003697881</t>
+          <t>47188882</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C001410731 - YAHUANA RIVERA DELIA HORTENCIA</t>
+          <t>C001572495 - NUNEZ JARA JOSE ELIZARDO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -11443,14 +11443,14 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>JR. SANTA ROSA(ESPALDAS DE HOTEL C NRO. 135 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>PJE. EL MERCADO NRO. 104 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>C004185355</t>
+          <t>C001413115</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>77039601</t>
+          <t>00370206</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C004185355 - CAMPOS INFANTES KAROL ISABEL</t>
+          <t>C001413115 - FARIAS DE RUIZ FABIOLA NOEMI</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -11495,14 +11495,14 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Jr santa rosa # 132</t>
+          <t>MCDO. MCDO ZARUMILLA (INTERIOR ) URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>C004183204</t>
+          <t>C001526507</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>00368678</t>
+          <t>45323624</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C004183204 - HERRERA AGUIRRE MAMERTO</t>
+          <t>C001526507 - ZURITA JIMENEZ EDINSON</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11547,14 +11547,14 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av el ejército #122 Zarumilla </t>
+          <t>AV. EX MERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>C004202682</t>
+          <t>C004193771</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11579,17 +11579,17 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>44130439</t>
+          <t>80273095</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>HUAMAN GARCIA AMELIA</t>
+          <t>C004193771 - TABOADA ZETA JOSE MANUEL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -11599,14 +11599,14 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prol 28 de julio s/n AA HH CAMPO AMOR </t>
+          <t xml:space="preserve">Psj el mercado N 108 cent Zarumilla </t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11621,22 +11621,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>C004202725</t>
+          <t>C001768136</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>00362206</t>
+          <t>10774237394</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>C004202725 - Tomaza Infantez Enrriquez De Herrera</t>
+          <t>C001768136 - LINARES SUAREZ ANGELA PATRICIA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -11651,14 +11651,14 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prol 28 de julio Mz 2 Lt 12 AAHH campo amor </t>
+          <t>CL. LETICIAS -EXT MERCADO ZARUMIL URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>C004192615</t>
+          <t>C004100567</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>46380371</t>
+          <t>45823572</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>C004192615 - HUANCAS PENA OVER</t>
+          <t>C004100567 - MATEO MAZA MADALI</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -11703,14 +11703,14 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>MZ 8-21 lt c AA HH campo Amor.psj la mar</t>
+          <t>Mcdo. Zarumilla Psto. 24</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11725,22 +11725,22 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>C004186969</t>
+          <t>C001768018</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>10003736615</t>
+          <t>74802061</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>C004186969 - GARCIA ZURITA OLINDA</t>
+          <t>C001768018 - CEDILLO LOPEZ LORENA DEL PILAR</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -11755,14 +11755,14 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Calle tingo maría Mz 09 lt 23 Aa hh campo amor</t>
+          <t>MCDO. BODEGA NRO. 5 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>C004188278</t>
+          <t>C001157395</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>46774825</t>
+          <t>03706464</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>C004188278 - Fany Suclupe Valdera</t>
+          <t>C001157395 - TALLEDO PE A LUCY</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11807,14 +11807,14 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calle las Mercedes MZ A9 Lt 18 AAHH campo amor </t>
+          <t>MERCADO DE ZARUMILLA URB. INTERIOR DE MERCADO PSTO. 09 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>C004202680</t>
+          <t>C001400704</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>70068082</t>
+          <t>00205425</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C004202680 - Angelica Milagritos Quinche Cruz</t>
+          <t>C001400704 - GOMEZ DE SERNA ANITA MARIA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11859,14 +11859,14 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av la marina Mz 7 Lt 13 AA HH Campo Amor </t>
+          <t>AV. INDEPENDENCIA NRO. 440 URB. CERCA A RADIO ACTIVA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>C004202729</t>
+          <t>C004172505</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>40496487</t>
+          <t>72412079</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C004202729 - Silvia Karina Maza Quezada</t>
+          <t>C004172505 - CORDOVA CORDOVA HERLINDA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -11911,14 +11911,14 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr puno Mz 11 Lt 3 AA HH Campo Amor </t>
+          <t xml:space="preserve">Int. Mercado zarumilla </t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>C004175995</t>
+          <t>C001378048</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>43918793</t>
+          <t>00371065</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C004175995 - ZARATE LOPEZ ANGGY LISSET</t>
+          <t>C001378048 - DELGADO SANCHEZ MELIDORO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -11963,14 +11963,14 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Av la marina 4ta cuadra Zarumilla ref.restaurant s</t>
+          <t>MCDO. MERCADO ZARUMILLA S/N URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>C001458876</t>
+          <t>C001018186</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>10003706589</t>
+          <t>10003627425</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C001458876 - CASTILLO ESTRADA JOSEFA</t>
+          <t>C001018186 - GARAY GONZALES FRANCISCO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -12015,14 +12015,14 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>CL. LIMA MZA. 13 LOTE. 24 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. INT MERCADO ZARUMILLA URB. ZARUMILLA PSTO. 12 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>C001460537</t>
+          <t>C001435909</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>80328433</t>
+          <t>17143614646</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>C001460537 - VINCES CABRERA LIZ VERONICA</t>
+          <t>C001435909 - DIAZ CHEVEZ ASTERIO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -12067,14 +12067,14 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>JR. LIMA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. PUESTO 06 MERCADO DE ZARUMILLA PSTO. 06 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>C004197169</t>
+          <t>C001158706</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>00373297</t>
+          <t>00369960</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>C004197169 - CRUZ LIZAMA CARLOTA</t>
+          <t>C001158706 - DELGADO SANCHEZ JESUS MARIA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -12119,14 +12119,14 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR Lámpa MZ 8 lt 3 AA HH CAMPO AMOR </t>
+          <t>MERCADO DE ZARUMILLA URB. ZARUMILLA PSTO. 30 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12141,22 +12141,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>C001475084</t>
+          <t>C001479795</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>10409724766</t>
+          <t>00371288</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C001475084 - SANTOS SANTOS CLORINDA</t>
+          <t>C001479795 - ZETA NAMUCHE ZAIDA ADRIANA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -12171,14 +12171,14 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>AV. CAMPO AMOR MZA. 13 LOTE. 5 Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. MERCADO ZARUMILLA NRO. 6 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12193,22 +12193,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>C004197270</t>
+          <t>C001130585</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>10421359615</t>
+          <t>16445546</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C004197270 - VARGAS LEON MERCEDES YAJAIRA</t>
+          <t>C001130585 - MAZA ZURITA SANTOS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -12223,14 +12223,14 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr lampa AAHH campo amor MZ13 L6 Zarumilla </t>
+          <t>AV. INTERIOR MERCADO ZARUMILLA URB. COSTADO DE ZURITA HUAMAN PSTO. 24 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12245,22 +12245,22 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>C004197176</t>
+          <t>C001730092</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>10700666978</t>
+          <t>00361652</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C004197176 - VILLEGAS GARCIA CLARA LIZ</t>
+          <t>C001730092 - TALLEDO PENA REYNA YSABEL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -12275,14 +12275,14 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av la Marina MZ 3 lt 21 AA HH campo Amor </t>
+          <t>AV. TUPAC AMARU NRO. 242 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12297,22 +12297,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>C001018367</t>
+          <t>C001672622</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>10003625091</t>
+          <t>43037512</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001018367 - CAMINO CARPIO NICANOR</t>
+          <t>C001672622 - DIOSES CUEVA DIOVALDO CLIMER</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -12327,14 +12327,14 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>CL. JIR INDEPENDENCIA N250 NRO. 250 MZA. MAZAA290 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. PRINCIPAL NRO. 223 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12349,22 +12349,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>C001475968</t>
+          <t>C001742395</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>10479276108</t>
+          <t>00364920</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001475968 - FERNANDEZ ALTAMIRANO, FLOR MARINA</t>
+          <t>C001742395 - VILELA NOLE CESAR ANTONIO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -12379,14 +12379,14 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>AV. ARICA NRO. 400 INT. 7 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. MERCADO DE ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12401,22 +12401,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>C001157367</t>
+          <t>C001366914</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>10434125591</t>
+          <t>00369656</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001157367 - ALAMO ZAPATA ROLANDO</t>
+          <t>C001366914 - ZURITA MATEO FAUSTINO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>AV. 28 DE JULIO NRO. 312 INT. 0001 URB. CERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. ZARUMILLA INT. 15 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12453,22 +12453,22 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>C001465397</t>
+          <t>C001420887</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>45923090</t>
+          <t>10003712007</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001465397 - VERA CRUZ JULIO BEYQUER</t>
+          <t>C001420887 - SALAZAR ATOCHE ESTHERCITA DINORA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -12483,14 +12483,14 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>AV. 28 DE JULIO NRO. 337 Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. MERCADO MODELO (ENTRADA PRINCI URB. ZARUMILLA PSTO. 28 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12505,22 +12505,22 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>C001484415</t>
+          <t>C004213910</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>10004679321</t>
+          <t>72675537</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001484415 - COARITE DE RODRIGUEZ MATILDE MARIA</t>
+          <t>C004213910 - RUGEL AMAYA MONICA MARGOT</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -12535,14 +12535,14 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>AV. CERCADO ZARUMILLA URB. CERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>Exterior mercado zarumilla - zarumilla</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12557,22 +12557,22 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>C001023416</t>
+          <t>C001674095</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>10805226124</t>
+          <t>74845473</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>C001023416 - ZETA NAMUCHE CARLOS ENRIQUE</t>
+          <t>C001674095 - REYES IZQUIERDO JOSEPH DARWIN</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -12587,14 +12587,14 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>MCDO. PUESTO NRO 08 MERCADO MUNICIP URB. ZARUMILLA MERCADO Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. MERCADO DE ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12609,22 +12609,22 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>C001519684</t>
+          <t>C004168510</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>10175615071</t>
+          <t>03209306</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C001519684 - CAJUSOL CHAPONAN FAUSTINO</t>
+          <t>C004168510 - MEZA VASQUEZ JORGE ALFREDO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -12639,14 +12639,14 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>AV. 28 DE JULIO NRO. 329 URB. COSTADO TIENDA CULQUI Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">Mercado Santa Rosa </t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12661,22 +12661,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>C001410730</t>
+          <t>C001682231</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>10003637846</t>
+          <t>45791115</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C001410730 - ROMERO GUERRERO LIDIA MARIA</t>
+          <t>C001682231 - OYOLA ALVITES JUAN DANIEL</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -12691,14 +12691,14 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>CL. PROLMAXIMILIANO MORAN NRO. 101 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. EX MERCADO ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12713,22 +12713,22 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>C001018369</t>
+          <t>C001722629</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>10003636378</t>
+          <t>41317230</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C001018369 - GARAY DE CAMPANA URSULINA</t>
+          <t>C001722629 - CAMPOS SEMINARIO LIZ LORENA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -12743,14 +12743,14 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>CL. JIR CASTILLA MARISCAL N233 NRO. 233 MZA. MAZAA020 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>JR. FRANSISCO BOLOGNESI ZARUMILL NRO. 505 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12765,22 +12765,22 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>C001408074</t>
+          <t>C001689498</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>20545367395</t>
+          <t>42984191</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001408074 - ORO PLAZA S.A.C.</t>
+          <t>C001689498 - MAZA HUAMAN DUBER</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12795,14 +12795,14 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>JR. TARAPACA Y CALLE TUMBES MZA. C LOTE. 01 URB. CERCA A FERRETERIA SILVA-ZARUM Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. EXT MERCADO DE ZARUMILLA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12817,22 +12817,22 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>C004202737</t>
+          <t>C001767082</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>40606089</t>
+          <t>10003713500</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C004202737 - Maria Del Pilar Ojeda Coronado</t>
+          <t>C001767082 - PORRAS SALDARRIAGA YUBICCY YICEL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12847,14 +12847,14 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cal lima Mz 12 Lt 1 AA HH Campo Amor </t>
+          <t>AV. MERCADO DE ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-08-25 00:00:00</t>
+          <t>2026-08-24 00:00:00</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12869,22 +12869,22 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>C004217948</t>
+          <t>C004184162</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>10002421092</t>
+          <t>71747219</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C004217948 - CESPEDES VINCES MARITZA BEATRIZ</t>
+          <t>C004184162 - CRIOLLO PORRAS JULIO ANTONIO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12899,14 +12899,14 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Cal santa rosa mz j lt 6 aa HH pozo elevado</t>
+          <t xml:space="preserve">Zarumilla, mercado x menestras </t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12921,22 +12921,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>C001025371</t>
+          <t>C004217946</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>10408572113</t>
+          <t>00373511</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001025371 - ALE YUNGA JHOVANY MAURICIO</t>
+          <t>C004217946 - GEORGINA ELIZABETH TUPEZ BURGOS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -12951,14 +12951,14 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>JR. MAXIMILIANO MORAN NRO. 316 Tumbes-Zarumilla-Zarumilla</t>
+          <t>Calle gardenias s/N esq con geranios/rest tollo</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12973,22 +12973,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>C001722805</t>
+          <t>C001410731</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>16724154</t>
+          <t>10003697881</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C001722805 - AVELLANEDA MONTENEGRO ROBERTO CARLOS</t>
+          <t>C001410731 - YAHUANA RIVERA DELIA HORTENCIA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -13003,14 +13003,14 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>JR. LETICIA ZARUMILLA NRO. 553 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>JR. SANTA ROSA(ESPALDAS DE HOTEL C NRO. 135 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13025,22 +13025,22 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>C001399804</t>
+          <t>C004185355</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>10728835295</t>
+          <t>77039601</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C001399804 - RUIZ VARILLAS CLAUDIA STEFANY</t>
+          <t>C004185355 - CAMPOS INFANTES KAROL ISABEL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -13055,14 +13055,14 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>JR. BOLOGNESI NRO. 401 URB. FTE A COLEGIO PIAGET Tumbes-Zarumilla-Zarumilla</t>
+          <t>Jr santa rosa # 132</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13077,22 +13077,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>C001022748</t>
+          <t>C004183204</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>10003698276</t>
+          <t>00368678</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C001022748 - HUARAC OCHOA JUAN DE DIOS</t>
+          <t>C004183204 - HERRERA AGUIRRE MAMERTO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -13107,14 +13107,14 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>JR. CAL FRANCISCO BOLOGNESI N315 NRO. 315 MZA. MAZAA260 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">Av el ejército #122 Zarumilla </t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13129,22 +13129,22 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>C001025194</t>
+          <t>C004202682</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>10003697644</t>
+          <t>44130439</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C001025194 - HUARAC DE MORAN ELIZABETH</t>
+          <t>HUAMAN GARCIA AMELIA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -13159,14 +13159,14 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>JR. CAL INDEPENDENCIA N509 NRO. 509 MZA. MAZAA010 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">Prol 28 de julio s/n AA HH CAMPO AMOR </t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>C001400697</t>
+          <t>C004202725</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>00364107</t>
+          <t>00362206</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C001400697 - SAAVEDRA DE MEDINA MARIA ISABEL</t>
+          <t>C004202725 - Tomaza Infantez Enrriquez De Herrera</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -13211,14 +13211,14 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>AV. INDEPENDENCIA NRO. 605 URB. COSTADO DE PELUQUERIA KASANDRA Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">Prol 28 de julio Mz 2 Lt 12 AAHH campo amor </t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13233,22 +13233,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>C001736882</t>
+          <t>C004192615</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>10002081437</t>
+          <t>46380371</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C001736882 - ARCAYA MORETTI ENMA LIDIA</t>
+          <t>C004192615 - HUANCAS PENA OVER</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>AV. TUMBES NRO. 205 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>MZ 8-21 lt c AA HH campo Amor.psj la mar</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13285,22 +13285,22 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>C004202782</t>
+          <t>C004186969</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>40287550</t>
+          <t>10003736615</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>C004202782 - Sara Noelia Bancayan Zarate</t>
+          <t>C004186969 - GARCIA ZURITA OLINDA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -13315,14 +13315,14 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr balta s/n AA HH CAMPO AMOR </t>
+          <t>Calle tingo maría Mz 09 lt 23 Aa hh campo amor</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>C004202544</t>
+          <t>C004188278</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>43187822</t>
+          <t>46774825</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>C004202544 - Elicia Cruz Tinedo</t>
+          <t>C004188278 - Fany Suclupe Valdera</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -13367,14 +13367,14 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calle Huancayo Mz C Lt 28 AA HH Campo Amor </t>
+          <t xml:space="preserve">Calle las Mercedes MZ A9 Lt 18 AAHH campo amor </t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>C004202531</t>
+          <t>C004202680</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>80488930</t>
+          <t>70068082</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>C004202531 - Vidolina Mateo Sayago</t>
+          <t>C004202680 - Angelica Milagritos Quinche Cruz</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -13419,14 +13419,14 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av Ancash Mz E 22 Lt 03 AA HH Campo Amor </t>
+          <t xml:space="preserve">Av la marina Mz 7 Lt 13 AA HH Campo Amor </t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>C004202523</t>
+          <t>C004202729</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -13451,12 +13451,12 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>76799078</t>
+          <t>40496487</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>C004202523 - Ana Karen Vergara Sullon</t>
+          <t>C004202729 - Silvia Karina Maza Quezada</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -13471,14 +13471,14 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Cal Moquegua s/n Ampliación nuevo Piura campo amor</t>
+          <t xml:space="preserve">Jr puno Mz 11 Lt 3 AA HH Campo Amor </t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13493,22 +13493,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>C001460538</t>
+          <t>C004175995</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>10432095008</t>
+          <t>43918793</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>C001460538 - ZAGACETA CASTILLO TANIA MERCEDES</t>
+          <t>C004175995 - ZARATE LOPEZ ANGGY LISSET</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -13523,14 +13523,14 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>NUEVO PIURA (100 MTROS DE POZA MZA. E18 LOTE. 22 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>Av la marina 4ta cuadra Zarumilla ref.restaurant s</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13545,22 +13545,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>C001515329</t>
+          <t>C001458876</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>43485289</t>
+          <t>10003706589</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>C001515329 - TINEO HUANCAS GRIMANESA</t>
+          <t>C001458876 - CASTILLO ESTRADA JOSEFA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -13575,14 +13575,14 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>CL. ILO NRO. 18 MZA. C Tumbes-Zarumilla-Zarumilla</t>
+          <t>CL. LIMA MZA. 13 LOTE. 24 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>C001458873</t>
+          <t>C001460537</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -13607,12 +13607,12 @@
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>44882524</t>
+          <t>80328433</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>C001458873 - SANTOS PEREZ BRUMILDA</t>
+          <t>C001460537 - VINCES CABRERA LIZ VERONICA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -13627,14 +13627,14 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>CL. LOS JARDINES MZA. 11 LOTE. 10 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
+          <t>JR. LIMA URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>C001464504</t>
+          <t>C004197169</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>43425953</t>
+          <t>00373297</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>C001464504 - GUEVARA CHANTA JAVIER</t>
+          <t>C004197169 - CRUZ LIZAMA CARLOTA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -13679,14 +13679,14 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>CRR. PANAMERICANA NORTE S/N URB. FTE A PUENTE LIMA - ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">JR Lámpa MZ 8 lt 3 AA HH CAMPO AMOR </t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>C001423019</t>
+          <t>C001475084</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>10003710179</t>
+          <t>10409724766</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>C001423019 - CHANTA GARCIA CRUZ ELENA</t>
+          <t>C001475084 - SANTOS SANTOS CLORINDA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -13731,14 +13731,14 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>CL. PANAMERICANA(ALTURA DEL PUENTE INT. 1 MZA. 09 LOTE. 28 URB. AH CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. CAMPO AMOR MZA. 13 LOTE. 5 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13753,22 +13753,22 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>C001400683</t>
+          <t>C004197270</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>80371250</t>
+          <t>10421359615</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>C001400683 - AMAYA GARAY JESUS MARIANELA</t>
+          <t>C004197270 - VARGAS LEON MERCEDES YAJAIRA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -13783,14 +13783,14 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>JR. TUMBES NRO. 516 URB. FTE RESTLAS DELICIAS DEL MAR Tumbes-Zarumilla-Zarumilla</t>
+          <t xml:space="preserve">Jr lampa AAHH campo amor MZ13 L6 Zarumilla </t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13805,22 +13805,22 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>C004202683</t>
+          <t>C004197176</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>00363445</t>
+          <t>10700666978</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C004202683 - Ana Isabel Dioses Guevara</t>
+          <t>C004197176 - VILLEGAS GARCIA CLARA LIZ</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -13835,14 +13835,14 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av panamericana N 269 AA HH CAMPO AMOR </t>
+          <t xml:space="preserve">Av la Marina MZ 3 lt 21 AA HH campo Amor </t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>C004065003</t>
+          <t>C001018367</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -13867,12 +13867,12 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>10002022511</t>
+          <t>10003625091</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>C004065003 - CABRERA PIZARRO CARMEN LUCY</t>
+          <t>C001018367 - CAMINO CARPIO NICANOR</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13887,14 +13887,14 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr huancayo Mz5 Lt4_AAHH campo amor </t>
+          <t>CL. JIR INDEPENDENCIA N250 NRO. 250 MZA. MAZAA290 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13909,22 +13909,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>C001458875</t>
+          <t>C001475968</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>45647702</t>
+          <t>10479276108</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C001458875 - CARBAJAL CHUJUTALLI JOSE DANIEL</t>
+          <t>C001475968 - FERNANDEZ ALTAMIRANO, FLOR MARINA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>CL. UCAYALI MZA. 14 LOTE. 12 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. ARICA NRO. 400 INT. 7 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13961,22 +13961,22 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>C001458874</t>
+          <t>C001157367</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>43450965</t>
+          <t>10434125591</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>C001458874 - SAAVEDRA SUAREZ JESSICA PAOLA</t>
+          <t>C001157367 - ALAMO ZAPATA ROLANDO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -13991,14 +13991,14 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>CL. LIMA MZA. 14 LOTE. 21 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. 28 DE JULIO NRO. 312 INT. 0001 URB. CERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>C004197151</t>
+          <t>C001465397</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>03356145</t>
+          <t>45923090</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>C004197151 - GARCIA MAZA IRMA</t>
+          <t>C001465397 - VERA CRUZ JULIO BEYQUER</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -14043,14 +14043,14 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>AA HH campo Amor JR ICA MZ 11 lt 26</t>
+          <t>AV. 28 DE JULIO NRO. 337 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>C001548917</t>
+          <t>C001484415</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>10700582626</t>
+          <t>10004679321</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C001548917 - CAMPOS LIZANA JOHANA SMITH</t>
+          <t>C001484415 - COARITE DE RODRIGUEZ MATILDE MARIA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -14095,14 +14095,14 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>AAHH CAMPO AMOR MZA. 12 LOTE. 16 Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. CERCADO ZARUMILLA URB. CERCADO ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>C001526524</t>
+          <t>C001023416</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>10426421891</t>
+          <t>10805226124</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C001526524 - BARRIENTOS MORAN DE REYES JAZMIN ANAIS</t>
+          <t>C001023416 - ZETA NAMUCHE CARLOS ENRIQUE</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -14147,14 +14147,14 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>JR. BOLOGNESI NRO. 321 URB. CENTRO -- ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>MCDO. PUESTO NRO 08 MERCADO MUNICIP URB. ZARUMILLA MERCADO Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -14169,22 +14169,22 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>C001530969</t>
+          <t>C001519684</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>03675241</t>
+          <t>10175615071</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C001530969 - SAAVEDRA POZO JENNY DEL PILAR</t>
+          <t>C001519684 - CAJUSOL CHAPONAN FAUSTINO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -14199,14 +14199,14 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>JR. BOLOGNESI NRO. 222 URB. CENTRO -- ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>AV. 28 DE JULIO NRO. 329 URB. COSTADO TIENDA CULQUI Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -14221,22 +14221,22 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>C004063881</t>
+          <t>C001410730</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>42899183</t>
+          <t>10003637846</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C004063881 - AVILA CORREA YANINA DEL PILAR</t>
+          <t>C001410730 - ROMERO GUERRERO LIDIA MARIA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -14251,14 +14251,14 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Mcdo zarumilla</t>
+          <t>CL. PROLMAXIMILIANO MORAN NRO. 101 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -14273,22 +14273,22 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>C004189484</t>
+          <t>C001018369</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>00370580</t>
+          <t>10003636378</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>C004189484 - Tarcila Huancas Santos</t>
+          <t>C001018369 - GARAY DE CAMPANA URSULINA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -14303,14 +14303,14 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>MZ 11 lt 10 AA HH campo Amor 6ta etapa</t>
+          <t>CL. JIR CASTILLA MARISCAL N233 NRO. 233 MZA. MAZAA020 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>C004192643</t>
+          <t>C001408074</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -14335,12 +14335,12 @@
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>10174311078</t>
+          <t>20545367395</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C004192643 - GUILLERMO ORDINOLA AMANDA</t>
+          <t>C001408074 - ORO PLAZA S.A.C.</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -14355,14 +14355,14 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ca Industrial MZ A lt 4 AAHH CAMPO AMOR </t>
+          <t>JR. TARAPACA Y CALLE TUMBES MZA. C LOTE. 01 URB. CERCA A FERRETERIA SILVA-ZARUM Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>C004186993</t>
+          <t>C004202737</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>42434625</t>
+          <t>40606089</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>C004186993 - Cristina Huancas Santos</t>
+          <t>C004202737 - Maria Del Pilar Ojeda Coronado</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -14407,14 +14407,14 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Calle los pinos mz A5 lt 01 AA hh campo amor</t>
+          <t xml:space="preserve">Cal lima Mz 12 Lt 1 AA HH Campo Amor </t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-08-26 00:00:00</t>
+          <t>2026-08-25 00:00:00</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -14429,22 +14429,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>C004202548</t>
+          <t>C004217948</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>44898927</t>
+          <t>10002421092</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>C004202548 - Clariza Huancas Pena</t>
+          <t>C004217948 - CESPEDES VINCES MARITZA BEATRIZ</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -14459,14 +14459,14 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av industrial Mz F Lt 6 AA HH LA ROCANA </t>
+          <t>Cal santa rosa mz j lt 6 aa HH pozo elevado</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -14481,22 +14481,22 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>C004208591</t>
+          <t>C001025371</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>00373885</t>
+          <t>10408572113</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C004208591 - GONZALES JIMENEZ PETRONILA DEL PILAR</t>
+          <t>C001025371 - ALE YUNGA JHOVANY MAURICIO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -14511,14 +14511,14 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calle Túpac Amaru N 215 Zarumilla </t>
+          <t>JR. MAXIMILIANO MORAN NRO. 316 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -14533,22 +14533,22 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>C001425486</t>
+          <t>C001722805</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>10030811734</t>
+          <t>16724154</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001425486 - ACHA CARMONA SEGUNDO EFRAIN</t>
+          <t>C001722805 - AVELLANEDA MONTENEGRO ROBERTO CARLOS</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -14563,14 +14563,14 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>CRR. PANAMERICANA(AAHH CAMPO) ALTUR MZA. 2 LOTE. 23 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
+          <t>JR. LETICIA ZARUMILLA NRO. 553 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>C004187032</t>
+          <t>C001399804</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -14595,12 +14595,12 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>10002407995</t>
+          <t>10728835295</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C004187032 - ESPINOZA VILLAR SANDRA FABIOLA</t>
+          <t>C001399804 - RUIZ VARILLAS CLAUDIA STEFANY</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -14615,14 +14615,14 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Aa hh campo amor sector rocana  mz f2 lt 1D</t>
+          <t>JR. BOLOGNESI NRO. 401 URB. FTE A COLEGIO PIAGET Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>C004202539</t>
+          <t>C001022748</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -14647,12 +14647,12 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>10000867999</t>
+          <t>10003698276</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C004202539 - TAPULLIMA FASABI EXILDA</t>
+          <t>C001022748 - HUARAC OCHOA JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -14667,14 +14667,14 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calle Bolívar Mz E2 Lt 12 AH LA ROCANA </t>
+          <t>JR. CAL FRANCISCO BOLOGNESI N315 NRO. 315 MZA. MAZAA260 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -14689,22 +14689,22 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>C004187006</t>
+          <t>C001025194</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>03233110</t>
+          <t>10003697644</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>C004187006 - Alejandrina Chanta Garcia</t>
+          <t>C001025194 - HUARAC DE MORAN ELIZABETH</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -14719,14 +14719,14 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Calle el bendito mz b lt 09 aa hh la rocana</t>
+          <t>JR. CAL INDEPENDENCIA N509 NRO. 509 MZA. MAZAA010 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>C004202546</t>
+          <t>C001400697</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>43970516</t>
+          <t>00364107</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C004202546 - Guadalupe De Jesus Villegas Aponte</t>
+          <t>C001400697 - SAAVEDRA DE MEDINA MARIA ISABEL</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -14771,14 +14771,14 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ca Juan Pablo II Mz C lt 12 AAHH la rocana </t>
+          <t>AV. INDEPENDENCIA NRO. 605 URB. COSTADO DE PELUQUERIA KASANDRA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>C004188250</t>
+          <t>C001736882</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>10725373533</t>
+          <t>10002081437</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>C004188250 - MANCHAY FERMIN ARBEL</t>
+          <t>C001736882 - ARCAYA MORETTI ENMA LIDIA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -14823,14 +14823,14 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>MZ  E5 lt  12 calle torre paz AA HH campo Amor</t>
+          <t>AV. TUMBES NRO. 205 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>C004188228</t>
+          <t>C004202782</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>17445559</t>
+          <t>40287550</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C004188228 - Rosa Yanet Morales Juarez</t>
+          <t>C004202782 - Sara Noelia Bancayan Zarate</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -14875,14 +14875,14 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>MZ E4 Lt 20 .calle Bolívar AA HH la rocana</t>
+          <t xml:space="preserve">Jr balta s/n AA HH CAMPO AMOR </t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>C004202542</t>
+          <t>C004202544</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -14907,12 +14907,12 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>48089131</t>
+          <t>43187822</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C004202542 - Teodolinda Perez Perez</t>
+          <t>C004202544 - Elicia Cruz Tinedo</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -14927,14 +14927,14 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Av industrial Mz F Lt 37 A H la rocana</t>
+          <t xml:space="preserve">Calle Huancayo Mz C Lt 28 AA HH Campo Amor </t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>C004188235</t>
+          <t>C004202531</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -14959,12 +14959,12 @@
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>46697499</t>
+          <t>80488930</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C004188235 - Lidia Lizana Huancas</t>
+          <t>C004202531 - Vidolina Mateo Sayago</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -14979,14 +14979,14 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t xml:space="preserve">MZ H Lt 19 Av industrial AA HH La rocana </t>
+          <t xml:space="preserve">Av Ancash Mz E 22 Lt 03 AA HH Campo Amor </t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -15001,22 +15001,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>C004217940</t>
+          <t>C004202523</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>10424161263</t>
+          <t>76799078</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C004217940 - BUSTAMANTE VASQUEZ CARMENCITA</t>
+          <t>C004202523 - Ana Karen Vergara Sullon</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -15031,14 +15031,14 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Aa HH los Cibeles mz c lt 17 espald del tecnologic</t>
+          <t>Cal Moquegua s/n Ampliación nuevo Piura campo amor</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-08-27 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -15053,22 +15053,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>C004188272</t>
+          <t>C001460538</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>47553845</t>
+          <t>10432095008</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C004188272 - Maritza Suclupe Valdera</t>
+          <t>C001460538 - ZAGACETA CASTILLO TANIA MERCEDES</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -15083,14 +15083,14 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t xml:space="preserve">MZ A lt 10 calle Quillabamba AA HH campo Amor </t>
+          <t>NUEVO PIURA (100 MTROS DE POZA MZA. E18 LOTE. 22 URB. ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -15105,22 +15105,22 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>C001540245</t>
+          <t>C001515329</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>20603539517</t>
+          <t>43485289</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA KARYMARA E.I.R.L.</t>
+          <t>C001515329 - TINEO HUANCAS GRIMANESA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -15130,19 +15130,19 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>JR. SIMON BOLIVAR NRO. 410 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CL. ILO NRO. 18 MZA. C Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>C004094813</t>
+          <t>C001458873</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -15167,12 +15167,12 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>43755776</t>
+          <t>44882524</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>TENORIO PALOMINO PAULA ROSA</t>
+          <t>C001458873 - SANTOS PEREZ BRUMILDA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -15182,19 +15182,19 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Jr simón bolívar 414</t>
+          <t>CL. LOS JARDINES MZA. 11 LOTE. 10 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>C001766073</t>
+          <t>C001464504</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>76985334</t>
+          <t>43425953</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>VARDALEZ CUEVA TANIA EXILDA</t>
+          <t>C001464504 - GUEVARA CHANTA JAVIER</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -15234,19 +15234,19 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>JR. BOLIVAR NRO. 409 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CRR. PANAMERICANA NORTE S/N URB. FTE A PUENTE LIMA - ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>C004193357</t>
+          <t>C001423019</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -15271,12 +15271,12 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>10002461884</t>
+          <t>10003710179</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>VIZCARRA TINEDO NORMA LUCY</t>
+          <t>C001423019 - CHANTA GARCIA CRUZ ELENA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -15286,19 +15286,19 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr Bolívar N 445 centro Tumbes </t>
+          <t>CL. PANAMERICANA(ALTURA DEL PUENTE INT. 1 MZA. 09 LOTE. 28 URB. AH CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -15313,22 +15313,22 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>C004183662</t>
+          <t>C001400683</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>10717023922</t>
+          <t>80371250</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>ZAPATA JIMENEZ MONICA FABIOLA DEL CARMEN</t>
+          <t>C001400683 - AMAYA GARAY JESUS MARIANELA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -15338,19 +15338,19 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t xml:space="preserve">jr abad puell cuadra 8, frente a la cochera de la </t>
+          <t>JR. TUMBES NRO. 516 URB. FTE RESTLAS DELICIAS DEL MAR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -15365,22 +15365,22 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>C001407954</t>
+          <t>C004202683</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>10002529799</t>
+          <t>00363445</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>MIRANDA ROMERO ROXANA CARMEN</t>
+          <t>C004202683 - Ana Isabel Dioses Guevara</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -15390,19 +15390,19 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>CL. FRANCISCO PIZARRO NRO. 224 URB. EL RECREO-CERCA AVNAVARRETE Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Av panamericana N 269 AA HH CAMPO AMOR </t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>C001408019</t>
+          <t>C004065003</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>10002125205</t>
+          <t>10002022511</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>FLORES DE SEVERINO MARICELA</t>
+          <t>C004065003 - CABRERA PIZARRO CARMEN LUCY</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -15442,19 +15442,19 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>CL. MAYOR NOVOA S/N URB. EL RECREO-ESQMIRAFLX PISCINA Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Jr huancayo Mz5 Lt4_AAHH campo amor </t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -15469,22 +15469,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>C001768135</t>
+          <t>C001458875</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>10400205260</t>
+          <t>45647702</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CAROLINA CAROLINA OLAYA CASTRO</t>
+          <t>C001458875 - CARBAJAL CHUJUTALLI JOSE DANIEL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -15494,19 +15494,19 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>JR. MIRAFLORES NRO. 341 Tumbes-Tumbes-Tumbes</t>
+          <t>CL. UCAYALI MZA. 14 LOTE. 12 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -15521,22 +15521,22 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>C004190465</t>
+          <t>C001458874</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>10002505555</t>
+          <t>43450965</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>CAMPOS FLORES NORA ELIZA</t>
+          <t>C001458874 - SAAVEDRA SUAREZ JESSICA PAOLA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -15546,19 +15546,19 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av mariscal castilla n 834 centro tumbes </t>
+          <t>CL. LIMA MZA. 14 LOTE. 21 URB. CAMPO AMOR Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>C001768399</t>
+          <t>C004197151</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>47250212</t>
+          <t>03356145</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>ORTEGA MANRIQUE DANIELI STEPHANIE</t>
+          <t>C004197151 - GARCIA MAZA IRMA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -15598,19 +15598,19 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>CL. PASAMAYITO NRO. 135 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>AA HH campo Amor JR ICA MZ 11 lt 26</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -15625,7 +15625,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>C004193603</t>
+          <t>C001548917</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>10002442600</t>
+          <t>10700582626</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>NOEL LABRIN AYLIN DANEISI</t>
+          <t>C001548917 - CAMPOS LIZANA JOHANA SMITH</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -15650,19 +15650,19 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR Jorge Herrera N 119 Barrio San José </t>
+          <t>AAHH CAMPO AMOR MZA. 12 LOTE. 16 Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -15677,22 +15677,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>C001407989</t>
+          <t>C001526524</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>00208942</t>
+          <t>10426421891</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>FARIAS MORAN ODELI MARTHA</t>
+          <t>C001526524 - BARRIENTOS MORAN DE REYES JAZMIN ANAIS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -15702,19 +15702,19 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>CL. TARATA NRO. 373 URB. CERCADO-COSTADO MINISTAGRIC Tumbes-Tumbes-Tumbes</t>
+          <t>JR. BOLOGNESI NRO. 321 URB. CENTRO -- ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>C001768392</t>
+          <t>C001530969</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15739,12 +15739,12 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>00216628</t>
+          <t>03675241</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>MARCHAN DE RUESTA ALICIA CONSUELO</t>
+          <t>C001530969 - SAAVEDRA POZO JENNY DEL PILAR</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -15754,19 +15754,19 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>AV. ARICA NRO. 230 URB. BARRIO SAN JOSE Tumbes-Tumbes-Tumbes</t>
+          <t>JR. BOLOGNESI NRO. 222 URB. CENTRO -- ZARUMILLA Tumbes-Zarumilla-Zarumilla</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>C001768391</t>
+          <t>C004063881</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -15791,12 +15791,12 @@
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>44211779</t>
+          <t>42899183</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>REYES SILVA NORMA DORILA</t>
+          <t>C004063881 - AVILA CORREA YANINA DEL PILAR</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -15806,19 +15806,19 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>AV. ARICA NRO. 235 URB. BARRIO SAN JOSE Tumbes-Tumbes-Tumbes</t>
+          <t>Mcdo zarumilla</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -15833,22 +15833,22 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>C004193593</t>
+          <t>C004189484</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>10002370072</t>
+          <t>00370580</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DIAZ DIAZ SOCORRO DEL PILAR</t>
+          <t>C004189484 - Tarcila Huancas Santos</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -15858,19 +15858,19 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Av tarapaca N 156 Barrio San José</t>
+          <t>MZ 11 lt 10 AA HH campo Amor 6ta etapa</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>C001708359</t>
+          <t>C004192643</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -15895,12 +15895,12 @@
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>10002255150</t>
+          <t>10174311078</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>MEDINA DIOS MIRIA</t>
+          <t>C004192643 - GUILLERMO ORDINOLA AMANDA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -15910,19 +15910,19 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>AV. PIURA NRO. 501 INT. 01 URB. CENTRO --TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Ca Industrial MZ A lt 4 AAHH CAMPO AMOR </t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -15937,22 +15937,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>C001748099</t>
+          <t>C004186993</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>20605274910</t>
+          <t>42434625</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA COMERCIAL POLO HOGAR S.R.L</t>
+          <t>C004186993 - Cristina Huancas Santos</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -15962,19 +15962,19 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>AV. SIMON BOLIVAR NRO. 312 INT. 1 URB. CERCADO Tumbes-Tumbes-Tumbes</t>
+          <t>Calle los pinos mz A5 lt 01 AA hh campo amor</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-08-28 00:00:00</t>
+          <t>2026-08-26 00:00:00</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -15989,22 +15989,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>C001763055</t>
+          <t>C004202548</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>10002550691</t>
+          <t>44898927</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>LUNA PALACIOS MARIA INES</t>
+          <t>C004202548 - Clariza Huancas Pena</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Tumbes (Tumbes)</t>
+          <t>Zarumilla (Zarumilla)</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>CL. HUASCAR NRO. 533 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Av industrial Mz F Lt 6 AA HH LA ROCANA </t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>C001612116</t>
+          <t>C001540245</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16051,12 +16051,12 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>10475395544</t>
+          <t>20603539517</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>IZQUIERDO GONZALES KATHERY SHIRLEY</t>
+          <t>DISTRIBUIDORA KARYMARA E.I.R.L.</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>CL. HUASCAR NRO. 530 Tumbes-Tumbes-Tumbes</t>
+          <t>JR. SIMON BOLIVAR NRO. 410 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>C001672625</t>
+          <t>C004094813</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>10711228603</t>
+          <t>43755776</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>BENITES ALVAREZ ROSA ISABEL</t>
+          <t>TENORIO PALOMINO PAULA ROSA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>AV. MARISCAL RAMON CASTILLA NRO. 644 Tumbes-Tumbes-Tumbes</t>
+          <t>Jr simón bolívar 414</t>
         </is>
       </c>
     </row>
@@ -16145,22 +16145,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>C001462468</t>
+          <t>C001766073</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>10002411569</t>
+          <t>76985334</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>GARCIA RUIZ SUSY MARISOL</t>
+          <t>VARDALEZ CUEVA TANIA EXILDA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>JR. ANDRES ARAUJO NRO. 103 URB. BARRIO BUENOS AIRES Tumbes-Tumbes-Tumbes</t>
+          <t>JR. BOLIVAR NRO. 409 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16197,22 +16197,22 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>C001480414</t>
+          <t>C004193357</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>80361690</t>
+          <t>10002461884</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>RISCO PARDO FRANZ EDWAR</t>
+          <t>VIZCARRA TINEDO NORMA LUCY</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO DE ABASTOS TUMBES NRO. 105 Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Jr Bolívar N 445 centro Tumbes </t>
         </is>
       </c>
     </row>
@@ -16249,22 +16249,22 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>C004221417</t>
+          <t>C004183662</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>75771464</t>
+          <t>10717023922</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DELGADO REYNA JONATAN MANUEL</t>
+          <t>ZAPATA JIMENEZ MONICA FABIOLA DEL CARMEN</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Interior mercado modelo s/n  tumbes</t>
+          <t xml:space="preserve">jr abad puell cuadra 8, frente a la cochera de la </t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>C001023702</t>
+          <t>C001407954</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>10003273305</t>
+          <t>10002529799</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>CALVA PARDO REMBERTO</t>
+          <t>MIRANDA ROMERO ROXANA CARMEN</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>AV. MER MODELO TUMBES I01 INT. 01 MZA. MAZAA036 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CL. FRANCISCO PIZARRO NRO. 224 URB. EL RECREO-CERCA AVNAVARRETE Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>C001017511</t>
+          <t>C001408019</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16363,12 +16363,12 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>10031247565</t>
+          <t>10002125205</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CULQUICONDOR ABAD DANIEL</t>
+          <t>FLORES DE SEVERINO MARICELA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>JR. AVE MRCDO MODELO I01 MZA. MAZAA30A URB. TUMBES MERCADO Tumbes-Tumbes-Tumbes</t>
+          <t>CL. MAYOR NOVOA S/N URB. EL RECREO-ESQMIRAFLX PISCINA Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>C001017864</t>
+          <t>C001768135</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>10002195173</t>
+          <t>10400205260</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>RAMIREZ DE TANDAZO DORINA</t>
+          <t>CAROLINA CAROLINA OLAYA CASTRO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>AV. MER MODELO ANEXO PSN MZA. MAZAA360 URB. TUMBES - MCDO Tumbes-Tumbes-Tumbes</t>
+          <t>JR. MIRAFLORES NRO. 341 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>C001022300</t>
+          <t>C004190465</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16467,12 +16467,12 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>10003703598</t>
+          <t>10002505555</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>LUPU VILELA JOSE EDIVAR</t>
+          <t>CAMPOS FLORES NORA ELIZA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>MERCADO MODELO PUESTO 23 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">Av mariscal castilla n 834 centro tumbes </t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>C001024801</t>
+          <t>C001768399</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>00255523</t>
+          <t>47250212</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>FALCONI VERA EDGAR</t>
+          <t>ORTEGA MANRIQUE DANIELI STEPHANIE</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>AV. MER MODELO ANEXO IINT PS/N INT. INT MZA. MAZAA031 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CL. PASAMAYITO NRO. 135 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>C001408023</t>
+          <t>C004193603</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -16571,12 +16571,12 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>10002145621</t>
+          <t>10002442600</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>ARRUNATEGUI DIOSES LUNILA ALODIA</t>
+          <t>NOEL LABRIN AYLIN DANEISI</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>JR. ALFONSO UGARTE NRO. 317 URB. CERCADO-CERCA HOTEL BLIAM Tumbes-Tumbes-Tumbes</t>
+          <t xml:space="preserve">JR Jorge Herrera N 119 Barrio San José </t>
         </is>
       </c>
     </row>
@@ -16613,22 +16613,22 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>C001451333</t>
+          <t>C001407989</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>20484122548</t>
+          <t>00208942</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>GINO QUIROZ E.I.R.L</t>
+          <t>FARIAS MORAN ODELI MARTHA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -16643,14 +16643,14 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>JR. BOLIVAR NRO. 105 URB. CENTRO - TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CL. TARATA NRO. 373 URB. CERCADO-COSTADO MINISTAGRIC Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -16665,22 +16665,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>C001453407</t>
+          <t>C001768392</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>10469800119</t>
+          <t>00216628</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>OLAYA SILVA RODIN GELLO</t>
+          <t>MARCHAN DE RUESTA ALICIA CONSUELO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -16695,14 +16695,14 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>AV. ALFONSO UGARTE NRO. 401 URB. BARRIO EL MILAGRO Tumbes-Tumbes-Tumbes</t>
+          <t>AV. ARICA NRO. 230 URB. BARRIO SAN JOSE Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -16717,22 +16717,22 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>C004217581</t>
+          <t>C001768391</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>10403228902</t>
+          <t>44211779</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>CLAVIJO IMAN VIANNEY</t>
+          <t>REYES SILVA NORMA DORILA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -16747,14 +16747,14 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AV. ARICA NRO. 235 URB. BARRIO SAN JOSE Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>C001768246</t>
+          <t>C004193593</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>10452028340</t>
+          <t>10002370072</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>MELIVEA OCUPA GUERRERO</t>
+          <t>DIAZ DIAZ SOCORRO DEL PILAR</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -16799,14 +16799,14 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>AV. ALFONSO UGARTE NRO. 434 Tumbes-Tumbes-Tumbes</t>
+          <t>Av tarapaca N 156 Barrio San José</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>C004217567</t>
+          <t>C001708359</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -16831,12 +16831,12 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>10468106243</t>
+          <t>10002255150</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>ROMERO MERINO LEIDY NOEMI</t>
+          <t>MEDINA DIOS MIRIA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -16851,14 +16851,14 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AV. PIURA NRO. 501 INT. 01 URB. CENTRO --TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>C001755662</t>
+          <t>C001748099</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>10002494308</t>
+          <t>20605274910</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>OCUPA ADRIANZEN OMAR ADAN</t>
+          <t>DISTRIBUIDORA COMERCIAL POLO HOGAR S.R.L</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -16903,14 +16903,14 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ NRO. 212 URB. BARRIO EL MILAGRO Tumbes-Tumbes-Tumbes</t>
+          <t>AV. SIMON BOLIVAR NRO. 312 INT. 1 URB. CERCADO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -16925,22 +16925,22 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>C001538026</t>
+          <t>C001763055</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>33819115</t>
+          <t>10002550691</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>ZEGARRA VIERA JUANA</t>
+          <t>LUNA PALACIOS MARIA INES</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -16955,14 +16955,14 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>AV. ALFONSO UGARTE URB. CENTRO - TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>CL. HUASCAR NRO. 533 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>C001017540</t>
+          <t>C001612116</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -16987,12 +16987,12 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>10002110488</t>
+          <t>10475395544</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>ROMERO PAUCAR FRANCISCA</t>
+          <t>IZQUIERDO GONZALES KATHERY SHIRLEY</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -17007,14 +17007,14 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>AV. OTR URB ANDRES ARAUJO MZ11 L MZA. MAZAA360 LOTE. 16 URB. TUMBES PUYANGO Tumbes-Tumbes-Tumbes</t>
+          <t>CL. HUASCAR NRO. 530 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -17029,22 +17029,22 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>C001766152</t>
+          <t>C001672625</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>77884270</t>
+          <t>10711228603</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>CALLE SAAVEDRA ANGEL WILFREDO</t>
+          <t>BENITES ALVAREZ ROSA ISABEL</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -17059,14 +17059,14 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>JR. ELOY URETA NRO. 357 Tumbes-Tumbes-Tumbes</t>
+          <t>AV. MARISCAL RAMON CASTILLA NRO. 644 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>C001420789</t>
+          <t>C001462468</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17091,12 +17091,12 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>10468137572</t>
+          <t>10002411569</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>ABAD VERA YIMY KENEDI</t>
+          <t>GARCIA RUIZ SUSY MARISOL</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -17111,14 +17111,14 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>AV. CIRCUNVALACION NRO. 203 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>JR. ANDRES ARAUJO NRO. 103 URB. BARRIO BUENOS AIRES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -17133,22 +17133,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>C001768022</t>
+          <t>C001480414</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>10711010608</t>
+          <t>80361690</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>MOROCHO LLACSAHUACHE EDITT</t>
+          <t>RISCO PARDO FRANZ EDWAR</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -17163,14 +17163,14 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>AV. MERCADO MODELO MZA. 752 LOTE. 1518 Tumbes-Tumbes-Tumbes</t>
+          <t>MCDO. MERCADO DE ABASTOS TUMBES NRO. 105 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>C001755659</t>
+          <t>C004221417</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17195,12 +17195,12 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>00239805</t>
+          <t>75771464</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>CEDILLO ALVAREZ WILLIAM</t>
+          <t>DELGADO REYNA JONATAN MANUEL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -17215,14 +17215,14 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ NRO. 270 Tumbes-Tumbes-Tumbes</t>
+          <t>Interior mercado modelo s/n  tumbes</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -17237,22 +17237,22 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>C001718929</t>
+          <t>C001023702</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>80247178</t>
+          <t>10003273305</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>VERA VERA GRICERIA</t>
+          <t>CALVA PARDO REMBERTO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -17267,14 +17267,14 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ NRO. 32 Tumbes-Tumbes-Tumbes</t>
+          <t>AV. MER MODELO TUMBES I01 INT. 01 MZA. MAZAA036 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -17289,22 +17289,22 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>C001755657</t>
+          <t>C001017511</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>45234727</t>
+          <t>10031247565</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>TINEO REYES JESUS MARIA</t>
+          <t>CULQUICONDOR ABAD DANIEL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -17319,14 +17319,14 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ Tumbes-Tumbes-Tumbes</t>
+          <t>JR. AVE MRCDO MODELO I01 MZA. MAZAA30A URB. TUMBES MERCADO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>C001024895</t>
+          <t>C001017864</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -17351,12 +17351,12 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>10002482270</t>
+          <t>10002195173</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>RIOS PAUCAR BEIMAR</t>
+          <t>RAMIREZ DE TANDAZO DORINA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -17371,14 +17371,14 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>AV. INTERIOR MERCADO MODELO URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>AV. MER MODELO ANEXO PSN MZA. MAZAA360 URB. TUMBES - MCDO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -17393,22 +17393,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>C001768248</t>
+          <t>C001022300</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>71073391</t>
+          <t>10003703598</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>CORTEZ CULQUICONDOR ANTONY</t>
+          <t>LUPU VILELA JOSE EDIVAR</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -17423,14 +17423,14 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>AV. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>MERCADO MODELO PUESTO 23 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -17445,22 +17445,22 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>C001375910</t>
+          <t>C001024801</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>10002020373</t>
+          <t>00255523</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>MERINO YAHUANA FLORICELDA DE JESUS</t>
+          <t>FALCONI VERA EDGAR</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -17475,14 +17475,14 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>MCDO. MERCADO MODELO TUMBES SECTOR URB. COSTADO DE MAURO MERINO PSTO. 461 Tumbes-Tumbes-Tumbes</t>
+          <t>AV. MER MODELO ANEXO IINT PS/N INT. INT MZA. MAZAA031 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>C001498881</t>
+          <t>C001408023</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -17507,12 +17507,12 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>10002384791</t>
+          <t>10002145621</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>LAZO TORRES MARIA EVA</t>
+          <t>ARRUNATEGUI DIOSES LUNILA ALODIA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -17527,14 +17527,14 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ EXTERIOR ME URB. SECTOR LA CUCHILLA Tumbes-Tumbes-Tumbes</t>
+          <t>JR. ALFONSO UGARTE NRO. 317 URB. CERCADO-CERCA HOTEL BLIAM Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-08-29 00:00:00</t>
+          <t>2026-08-28 00:00:00</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>C001359908</t>
+          <t>C001451333</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>10068318322</t>
+          <t>20484122548</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>ROMERO VASQUEZ AMELIDA TERESA</t>
+          <t>GINO QUIROZ E.I.R.L</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>CL. FRANCISCO IBAÑEZ NRO. 248 URB. CERCA A JIMENEZ LAZO DORIS Tumbes-Tumbes-Tumbes</t>
+          <t>JR. BOLIVAR NRO. 105 URB. CENTRO - TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17601,7 +17601,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>C001639216</t>
+          <t>C001453407</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -17611,12 +17611,12 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>10415050718</t>
+          <t>10469800119</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>CESAR PAZ CORNEJO REYES</t>
+          <t>OLAYA SILVA RODIN GELLO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>AV. MERCADO MODELO URB. SECTOR -- CUCHILLA PSTO. 462 Tumbes-Tumbes-Tumbes</t>
+          <t>AV. ALFONSO UGARTE NRO. 401 URB. BARRIO EL MILAGRO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17653,7 +17653,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>C004159259</t>
+          <t>C004217581</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -17663,12 +17663,12 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>20612822698</t>
+          <t>10403228902</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LOS LICENCIADOS</t>
+          <t>CLAVIJO IMAN VIANNEY</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>AV. FRANCISCO IBAÑEZ Nº 212</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>C001025409</t>
+          <t>C001768246</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -17715,12 +17715,12 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>10002523791</t>
+          <t>10452028340</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>CHACALTANA CRISANTO CARLOS UBALDO</t>
+          <t>MELIVEA OCUPA GUERRERO</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>CL. FRANCISCO IBA EZ NRO. 292 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>AV. ALFONSO UGARTE NRO. 434 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17757,22 +17757,22 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>C001543443</t>
+          <t>C004217567</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>40577068</t>
+          <t>10468106243</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>ORDINOLA HERRERA JOSE LUIS</t>
+          <t>ROMERO MERINO LEIDY NOEMI</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>AV. MERCADO MODELO TUMBES INT. 32 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17809,22 +17809,22 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>C001176472</t>
+          <t>C001755662</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>43947205</t>
+          <t>10002494308</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>PARDO PAUCAR MILTON</t>
+          <t>OCUPA ADRIANZEN OMAR ADAN</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>MERCADO MODELO TUMBES URB. INTERIOR MERCADO Tumbes-Tumbes-Tumbes</t>
+          <t>AV. FRANCISCO IBAÑEZ NRO. 212 URB. BARRIO EL MILAGRO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>C001768408</t>
+          <t>C001538026</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -17871,12 +17871,12 @@
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>44825284</t>
+          <t>33819115</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>GUARNIZO BALLADARES EDGAR DICK LEE</t>
+          <t>ZEGARRA VIERA JUANA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>CL. ELOY URETA NRO. 12 INT. 12 Tumbes-Tumbes-Tumbes</t>
+          <t>AV. ALFONSO UGARTE URB. CENTRO - TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17913,22 +17913,22 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>C004176583</t>
+          <t>C001017540</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>00219959</t>
+          <t>10002110488</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>REA PANGALIMA MARIA MAGDALENA</t>
+          <t>ROMERO PAUCAR FRANCISCA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercado tumbes, Av piura </t>
+          <t>AV. OTR URB ANDRES ARAUJO MZ11 L MZA. MAZAA360 LOTE. 16 URB. TUMBES PUYANGO Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>C004187416</t>
+          <t>C001766152</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -17975,12 +17975,12 @@
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>00221680</t>
+          <t>77884270</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Gloria Elva Benites Aponte</t>
+          <t>CALLE SAAVEDRA ANGEL WILFREDO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t xml:space="preserve">JR Agusto velegia N 192 Barrio El Milagro </t>
+          <t>JR. ELOY URETA NRO. 357 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -18017,22 +18017,22 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>C004187372</t>
+          <t>C001420789</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>00256156</t>
+          <t>10468137572</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Sara Maria Parrales Oyola</t>
+          <t>ABAD VERA YIMY KENEDI</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Prol jose jimenez 210 Barrio El Milagro</t>
+          <t>AV. CIRCUNVALACION NRO. 203 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -18069,22 +18069,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>C004187403</t>
+          <t>C001768022</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>40571182</t>
+          <t>10711010608</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Olga Maria Rujel Atoche</t>
+          <t>MOROCHO LLACSAHUACHE EDITT</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Av Alfonso Ugarte N  1002 barrio el milagro </t>
+          <t>AV. MERCADO MODELO MZA. 752 LOTE. 1518 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -18121,22 +18121,22 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>C001660986</t>
+          <t>C001755659</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>10471950055</t>
+          <t>00239805</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>ANDREA DEL ROSARIO GUEVARA CASTILLO</t>
+          <t>CEDILLO ALVAREZ WILLIAM</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>CL. SIETE DE ENERO NRO. 306 URB. CENTRO --TUMBES Tumbes-Tumbes-Tumbes</t>
+          <t>AV. FRANCISCO IBAÑEZ NRO. 270 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
@@ -18173,42 +18173,978 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
+          <t>C001718929</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>80247178</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>VERA VERA GRICERIA</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>AV. FRANCISCO IBAÑEZ NRO. 32 Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>C001755657</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>45234727</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>TINEO REYES JESUS MARIA</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>AV. FRANCISCO IBAÑEZ Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>C001024895</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>10002482270</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>RIOS PAUCAR BEIMAR</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>AV. INTERIOR MERCADO MODELO URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>C001768248</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>71073391</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>CORTEZ CULQUICONDOR ANTONY</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>AV. TUMBES Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>C001375910</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>10002020373</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>MERINO YAHUANA FLORICELDA DE JESUS</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MCDO. MERCADO MODELO TUMBES SECTOR URB. COSTADO DE MAURO MERINO PSTO. 461 Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>C001498881</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>10002384791</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>LAZO TORRES MARIA EVA</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>AV. FRANCISCO IBAÑEZ EXTERIOR ME URB. SECTOR LA CUCHILLA Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>C001359908</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>10068318322</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ROMERO VASQUEZ AMELIDA TERESA</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>CL. FRANCISCO IBAÑEZ NRO. 248 URB. CERCA A JIMENEZ LAZO DORIS Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>C001639216</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>10415050718</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>CESAR PAZ CORNEJO REYES</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>AV. MERCADO MODELO URB. SECTOR -- CUCHILLA PSTO. 462 Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>C004159259</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>20612822698</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA LOS LICENCIADOS</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>AV. FRANCISCO IBAÑEZ Nº 212</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>C001025409</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>10002523791</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>CHACALTANA CRISANTO CARLOS UBALDO</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>CL. FRANCISCO IBA EZ NRO. 292 URB. TUMBES Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>C001543443</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>40577068</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ORDINOLA HERRERA JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>AV. MERCADO MODELO TUMBES INT. 32 URB. CENTRO TUMBES Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>C001176472</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>43947205</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>PARDO PAUCAR MILTON</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>MERCADO MODELO TUMBES URB. INTERIOR MERCADO Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>C001768408</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>44825284</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>GUARNIZO BALLADARES EDGAR DICK LEE</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>CL. ELOY URETA NRO. 12 INT. 12 Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>C004176583</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>00219959</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>REA PANGALIMA MARIA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mercado tumbes, Av piura </t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>C004187416</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>00221680</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Gloria Elva Benites Aponte</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JR Agusto velegia N 192 Barrio El Milagro </t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>C004187372</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>00256156</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Sara Maria Parrales Oyola</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Prol jose jimenez 210 Barrio El Milagro</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>C004187403</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>40571182</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Olga Maria Rujel Atoche</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Av Alfonso Ugarte N  1002 barrio el milagro </t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>C001660986</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>10471950055</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>ANDREA DEL ROSARIO GUEVARA CASTILLO</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>TUMBES</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Tumbes (Tumbes)</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>CL. SIETE DE ENERO NRO. 306 URB. CENTRO --TUMBES Tumbes-Tumbes-Tumbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ATUQ DEX S.A.C.</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
           <t>C001114262</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
+      <c r="E361" t="inlineStr">
         <is>
           <t>RUC</t>
         </is>
       </c>
-      <c r="F343" s="2" t="inlineStr">
+      <c r="F361" s="2" t="inlineStr">
         <is>
           <t>10408803654</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
+      <c r="G361" t="inlineStr">
         <is>
           <t>MARCHAN SEMINARIO ZORAIDA</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
+      <c r="H361" t="inlineStr">
         <is>
           <t>TUMBES</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
+      <c r="I361" t="inlineStr">
         <is>
           <t>Tumbes (Tumbes)</t>
         </is>
       </c>
-      <c r="J343" t="inlineStr">
+      <c r="J361" t="inlineStr">
         <is>
           <t>JR. JR 07 DE ENERO NRO. 202 Tumbes-Tumbes-Tumbes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J343"/>
+  <autoFilter ref="A1:J361"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>